--- a/frontend/public/primer.xlsx
+++ b/frontend/public/primer.xlsx
@@ -420,14 +420,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -463,21 +463,21 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Бумага для офисной техники А4</t>
+          <t>Ноутбук</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Плотность 80 г/м2, 500 листов в пачке, белизна не менее 146 %</t>
+          <t>Диагональ экрана: не менее 15.6 дюйма; оперативная память 16 ГБ; тип накопителя SSD; разрешение экрана Full HD; количество ядер процессора 4</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>пачка</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -486,12 +486,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Мыло туалетное твердое</t>
+          <t>Мышь компьютерная</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Масса 100 г, без отдушки</t>
+          <t>Тип подключения: беспроводной; интерфейс USB; питание от аккумулятора; мультифункциональные клавиши: да</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -500,7 +500,7 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -509,21 +509,21 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Перчатки смотровые нитриловые неопудренные</t>
+          <t>Клавиатура</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Размер M, нестерильные</t>
+          <t>Тип подключения: проводная; полноразмерная; интерфейс USB; длина кабеля 1,6 м</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>пара</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>200</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -532,12 +532,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Шприц инъекционный трехкомпонентный</t>
+          <t>Тетрадь ученическая школьная</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Объем 5 мл, с иглой</t>
+          <t>Линовка: линейка; 12 листов</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
     </row>
     <row r="6">
@@ -555,21 +555,21 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Кефир</t>
+          <t>Папка картонная</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Массовая доля жира 2,5 %, упаковка 1 л</t>
+          <t>Формат А3; папка-обложка без скоросшивателя</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>л</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7">
@@ -578,21 +578,21 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Ноутбук</t>
+          <t>Полотенце бумажное</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Диагональ экрана 15.6 дюйм, оперативная память 16 ГБ, SSD 512 ГБ</t>
+          <t>Форма выпуска: лист; 50 листов в упаковке</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>упак</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8">
@@ -601,12 +601,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Картридж для лазерного принтера</t>
+          <t>Лампа светодиодная</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Черный, ресурс не менее 1600 страниц</t>
+          <t>Двухцокольная; мощность 10 Вт; цоколь G23; цветовая температура 2700 К</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9">
@@ -624,12 +624,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Стол письменный</t>
+          <t>Телевизор</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Длина 1200 мм, ширина 600 мм, ЛДСП</t>
+          <t>Тип экрана QLED; разрешение 8K UHD; диагональ 40 дюймов; Smart TV: да; 3D-экран: да</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -638,7 +638,76 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Масло сливочное</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Сладко-сливочное, Крестьянское, высший сорт, несоленое</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Кефир</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Тип молочного сырья: нормализованное молоко; 2,5 процента</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>л</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Услуги частной охраны (выставление поста охраны)</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Охрана имущества и обеспечение пропускного режима на объектах с требованиями к антитеррористической защищенности</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>усл. ед</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
